--- a/cds/mm_indonesia-5year-cds.xlsx
+++ b/cds/mm_indonesia-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="661">
   <si>
     <t>Date</t>
   </si>
@@ -1983,6 +1983,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -2332,7 +2347,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B660"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7573,6 +7588,46 @@
       </c>
       <c r="B655" s="3">
         <v>85.1543</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B656" s="3">
+        <v>91.9918</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B657" s="3">
+        <v>98.3204</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B658" s="3">
+        <v>104.2281</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B659" s="3">
+        <v>98.5171</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B660" s="3">
+        <v>88.0194</v>
       </c>
     </row>
   </sheetData>
